--- a/docs/DS粗灰预测-疑问与决策.xlsx
+++ b/docs/DS粗灰预测-疑问与决策.xlsx
@@ -9,11 +9,15 @@
   <sheets>
     <sheet name="一、现状事实" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="二、疑问清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="三、四因子三条路线" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="四、因子想法核对" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="五、训练范围对照" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="六、502灰分配对明细" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="七、回答方式" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Q6-方向说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Q3-验收实测" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Q3-结论" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Q7-固定供给-已落地" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="三、四因子三条路线" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="四、因子想法核对" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="五、训练范围对照" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="六、502灰分配对明细" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="七、回答方式" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,27 +638,286 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>按月看：粗灰样本能不能在同一时段对上 502 灰分（3h 内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>粗灰条数</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>≤1h</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>≤3h</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>≤6h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>怎么回这份表（★你已回复 2026-09-24 一轮：Q1/Q2/Q3/Q4/Q7 已定，Q5/Q8 待现场确定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>方式</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>做法</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>已收到的答复</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Q1 不做（维持 10 因子）｜Q2 A（下一条采样点）｜Q3 A（打赢取均值/在线平滑）｜Q4 C（全部数据）｜Q7 A（固定目录供给）；Q5/Q8 待确定；Q6 需要我先解释（已补说明页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>需要你继续回的</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>① Q6：A 接入操作提示 / B 先只展示（我建议）/ C 先关掉；② Q5：采样后约几小时能拿到化验结果；③ Q8：有没有在线或每班 1 次的灰分数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>现场怎么问（Q5）</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>问化验室：“粗精煤泥 315 灰分从取样到出结果、再到录入大约几小时？白天和夜班一样吗？”</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>现场怎么问（Q8）</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>问仪表/工艺：“粗精煤泥灰分有没有在线测量？如果没有，化验能不能从每天 4~5 次加到每班 1 次？”</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>直接填表</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>在「二、疑问清单」的「你的回答」列改字即可（我已把你上一轮的原文保留在表里，重跑生成不会丢）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>对话回答</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>直接在对话里说“Q6 选 B、Q5 是 4 小时”也完全可以</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>本轮已默认执行</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>密度特征（你已指示搁置）、502 灰分因子（证据不足）、四因子（不做）、固定供给（Q7=A 已落地并验证）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>待你回答的疑问（在「你的选择」列填 A/B/C，或直接在对话里说）</t>
+          <t>待你回答的疑问（★已收到你 2026-09-24 的答复，原文在「你的回答」列）</t>
         </is>
       </c>
     </row>
@@ -686,7 +949,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>你的选择</t>
+          <t>你的回答</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>状态 / 我的处理</t>
         </is>
       </c>
     </row>
@@ -716,7 +984,16 @@
           <t>A（若你希望 DS 的向前成绩好看一点）；工作量约半天，含对拍复核</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>不做，现在只是数据量少10因子数据不好看</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>已按「维持 10 因子」处理：本轮不改模型；等粗灰样本 ≥300 条时用同一套向前验收复算再议</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -744,7 +1021,16 @@
           <t>先确认目标口径再谈精度，否则做出来也不是你要的那个数</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>已按 A（预测下一条采样点的 315 灰分）——与现行模型口径一致，无需改动</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -772,7 +1058,16 @@
           <t>A（现实且可验收）；若你要 B/C，需要更细的在线数据（见 Q7/Q8）</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>验收线=打赢取均值/在线平滑基线。★本轮实测：现有数据下达不到（见「Q3-验收实测」）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -800,7 +1095,16 @@
           <t>A + 定期加新数据（留出最新一两个月做检验窗口）</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>已记录：训练范围=全部。注意此时系统只能给「留尾参考」，没有真向前窗口（页面已标注）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -828,7 +1132,16 @@
           <t>若滞后 ≥ 数小时，在线校正基本不可行，重心应放在方向信号</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>待确定</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>需要现场问化验室：315 灰分从采样到出结果/录入通常几小时</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -856,7 +1169,16 @@
           <t>B 先展示一段时间，等你观察后再决定是否接入</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>我不明白你的意思</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>已补「Q6-方向说明」页：用大白话+例子解释这个开关是什么、两个选项的后果</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -884,7 +1206,16 @@
           <t>A（改动最小、立刻提升向前验收的样本量）</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>已落地：投放目录 + 文件名识别 + 一键导入 + 导入后归档（见「Q7-固定供给-已落地」）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -912,7 +1243,556 @@
           <t>A 或 B —— 这是精度上限的关键</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>待确定</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>需要现场确认：粗精煤泥灰分有没有在线测量，或能否加密到每班 1 次</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Q6 用大白话再说一遍：这条“方向”是什么、接进操作提示会变成什么样子</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>这条“方向”是什么</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>系统每次化验后，会算一句话：「下一次化验的粗精煤泥灰分，相对这一次，是偏涨还是偏跌」。历史回算的命中率约 0.76（95% 区间 0.64~0.88），比“瞎猜/惯性猜”明显好。它**只给方向、不给幅度**，也不是“一定会涨/跌”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>现在它在哪</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>只在粗精煤泥页的「向前验证」区块里显示一行文字，例如「下一读数方向：命中 0.762……」。它**不影响**页面上给你的密度建议 —— 加不加密度、加多少，还是按现在那套规则算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>“接进操作提示”是什么意思</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>就是把这句话变成一个**动作提示**。举例：现在方向判为“偏涨”，页面上就会多一行：「粗灰方向偏涨 → 可考虑把重介密度小幅上调（例如 +0.005）」；判为“偏跌”就提示「可考虑小幅下调」。也就是让方向去**推动**密度建议。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>为什么我不建议马上接（选 B）</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>① 方向只说涨跌、没有幅度，而密度要的是“调多少”；② 灰分涨跌的成因很多（原煤变化、系统开停、脱粉切换），不一定是密度造成的，直接连成操作建议可能把人带偏；③ 这条信号是 2026-09-23 才做出来的，现场还没观察过它的实际表现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>我的建议（仍是 B）</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>先在页面上展示一两个月，你和操作工对着实际化验结果看它准不准；等你有把握了，再告诉我“可以接”，我再把它连进密度建议（那时还要一起定：方向偏涨时到底动不动密度、动多少）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>你要怎么回答</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>A 现在就接进操作提示；B 先只展示（我建议这个）；C 先关掉别显示。回一句 A/B/C 即可。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>按你定的验收线（打赢取均值/在线平滑）实测：现有数据下达不到（2026-09-24 现算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>锁定检验窗 MAE</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>锁定窗是否达标</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>开发侧向前窗 MAE</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>开发侧是否达标</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>两窗都达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>模型+校正k20 再混EWMA .5</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1.456</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2.308</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>混合 0.25·模型+EWMA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1.470</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2.184</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>混合 0.25·模型+近5条</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1.509</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2.233</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>混合 0.50·模型+EWMA</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1.523</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2.210</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>在线·EWMA0.2</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1.549</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2.219</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>混合 0.50·模型+近5条</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2.195</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>在线·近5条均值</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>1.568</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2.334</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>模型+残差校正k30</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1.650</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2.606</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>模型+残差校正k20</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>1.664</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2.651</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>模型+残差校正k10</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>1.711</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2.808</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>取训练均值</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>1.744</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2.095</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>模型(10因子MLR)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>1.814</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2.564</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>未达标</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>—— 参考：各窗最强基线 ——</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>1.549（在线·EWMA0.2）</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>基线</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2.095（取训练均值）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>基线</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -922,7 +1802,244 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="102" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Q3 的结论与下一步：模型现在做不到“打赢基线”，瓶颈在数据密度</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>实验做了什么</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>在同一个真向前窗口上，试了“模型 + 在线残差校正（近10/20/30条）”“模型与在线平滑按 0.25/0.5 混合”共 8 种组合，看有没有哪种能同时打赢两个窗口的最强基线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>锁定窗（9-04~9-21，50 条）：最好的是「模型+校正k20 再混EWMA」1.456，确实打赢了该窗最强基线 在线·EWMA0.2 1.549；但同一个方法在开发侧窗（8-23~9-03，42 条）是 2.308，输给该窗最强基线 取训练均值 2.095。→ 没有任何一种组合能在两个窗口同时达标（无）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>为什么会这样</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>两个检验窗的“赢家”不同：开发侧窗里“取训练均值”最准（2.095），锁定窗里“在线指数平滑”最准（1.549）。差别在于检验期的中枢离训练中枢远近 —— 这人事先不知道。模型的价值既没稳定超过常数基线，也没稳定超过“看最近几次读数”的做法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>和你的判断一致</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>你说“现在只是数据量少”——实测支持这个判断：数据点太稀（每天 4~5 个瞬时值、相邻中位 2.6 小时），水平预测的可达精度基本被“取均值/看最近几次”锁死。要把水平预测做上去，主要靠 Q7（样本量）与 Q8（更密或在线数据），而不是换因子或换算法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>因此我的建议</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>① 水平预测：先按现有 10 因子跑着，页面上如实标“向前 MAE + 基线对照”，不承诺精度；② 真正可用的前向信号是方向（0.76），先把方向在页面上养一段时间（见 Q6）；③ 等粗灰样本到 300 条以上，用同一套验收复算（工具已就绪：evaluate_ds_forward.py / 页面区块）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>复盘触发条件</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>粗灰样本 ≥300 条（约再导 2 批）或下次导入后 → 重跑 evaluate_ds_forward.py，看模型是否开始打赢基线；若仍打不赢，则说明瓶颈确实是数据密度，应推动 Q8。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Q7=A 已落地：投放目录 + 文件名识别 + 一键导入 + 导入后归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>约定目录</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\25925\Desktop\web(2)导入数据\自动导入（脚本里 DROP_DIR，可改）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>放什么</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>三类表各放一个 xlsx：文件名含「粗精煤泥」→ 粗灰表；含「灰分」+「密度」→ 灰分密度表；含「浮精」→ 浮精表。列序与现在给的模板一致即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>一条命令</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>python backend/scripts/import_new_batch.py --scan-dir "C:\Users\25925\Desktop\web(2)导入数据\自动导入"（只看计划）
+python backend/scripts/import_new_batch.py --scan-dir &lt;同一目录&gt; --apply（真正导入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>每类取**修改时间最新**的文件；~$ 临时文件与小于 4 KB 的异常文件自动忽略；导入成功后把用过的文件移到 自动导入\已导入\&lt;时间戳&gt;\，下轮不会重复导入；解析失败的那一类**不归档**（留在原处，修正后重跑即可），另外两类照常导入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>口径不变</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>与 2026-09-24 这批完全一致：粗灰只导有效行（不做日期填充）；灰分密度只导 A 系统、密度写 1 的记 NULL；与库内旧行近似重叠时以新文件为准（--overlap replace，窗口 60 分钟）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>已验证</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>临时库=导入前备份 + 临时投放目录实跑：① 不放 --apply 时零写入、零归档；② 目录里混入 1 KB 垃圾文件与 7 KB“最新但内容是垃圾”的文件时，只有该类别被跳过并留痕，其余两类正常；③ 正常导入复现生产结果（粗灰 152→205、灰分密度 360→543、浮精 17→31），三个源文件归档，生产库未被改动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>建议节奏</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>每周或每次拿到化验数据就丢进目录跑一次；导入后页面的「向前验证」会随数据自动更新。若希望完全不用敲命令，可以再做一个双击运行的 .bat（说一声我来加）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1061,7 +2178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1157,7 +2274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1351,226 +2468,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>按月看：粗灰样本能不能在同一时段对上 502 灰分（3h 内）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>粗灰条数</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>≤1h</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>≤3h</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>≤6h</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>怎么回这份表</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>方式</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>做法</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>直接填表</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>在「二、疑问清单」的「你的选择」列填 A/B/C（或写文字），把文件发回即可</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>对话回答</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>直接在对话里说“Q1 选 A、Q2 是日均值……”也完全可以，我会同步回表并落到代码/文档</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>只答关键项</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>最少只需回答 Q1（四因子）与 Q2（预测目标口径）——其余可以边做边定</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>本轮已默认执行</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>密度特征（你已指示搁置）、502 灰分因子（证据不足）、B 系统密度补导（等你确认）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/DS粗灰预测-疑问与决策.xlsx
+++ b/docs/DS粗灰预测-疑问与决策.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Q1 不做（维持 10 因子）｜Q2 A（下一条采样点）｜Q3 A（打赢取均值/在线平滑）｜Q4 C（全部数据）｜Q7 A（固定目录供给）；Q5/Q8 待确定；Q6 需要我先解释（已补说明页）</t>
+          <t>Q1 不做（维持 10 因子）｜Q2 A（下一条采样点）｜Q3 A（打赢取均值/在线平滑）｜Q4 C（全部数据）｜Q6 B（方向只展示观察）｜Q7 A（固定目录供给）；Q5/Q8 待确定</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>① Q6：A 接入操作提示 / B 先只展示（我建议）/ C 先关掉；② Q5：采样后约几小时能拿到化验结果；③ Q8：有没有在线或每班 1 次的灰分数据</t>
+          <t>① Q5：采样后约几小时能拿到化验结果；② Q8：有没有在线或每班 1 次的灰分数据</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>我不明白你的意思</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>已补「Q6-方向说明」页：用大白话+例子解释这个开关是什么、两个选项的后果</t>
+          <t>已按 B 落地：方向只在页面展示观察，不接入密度建议；并新增「最近判断 涨✔跌✘」清单（近 20 次逐条）+ 页面上明确写「当前只展示、不参与密度建议」</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1357,10 +1357,58 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>★你的答复：B（2026-09-24）</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>已按 B 落地，并且把“观察”做成看得见的东西：粗精煤泥页「向前验证」区块新增一行「最近判断：涨✔ 跌✔ 涨✘ …（近20次命中 0.xxx）」，鼠标悬停能看到每次的时间、预测与实际；同一区块里明确写「当前只展示、不参与密度建议」。方向怎么算、检验窗口是什么，都写在同页说明里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>什么时候再回来看</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>建议积累 1~2 个月（约 30~60 个新采样点）后复盘：看「最近判断」的实际命中是否还在 0.7 附近。若明显下滑，说明机理变了（原煤/工艺变化），要重算；若稳定，再来定“接入操作提示”怎么接。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>★观察时先留意这一条（实测）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>方向的命中率跟【模型新鲜度】关系很大：同一个 9 月窗口，训练截止 9-03 的模型最近 20 次命中 0.750，而训练截止 8-22 的（更旧的）模型最近 20 次只有 0.550（接近瞎猜），整体命中也由 0.762 降到 0.667。→ 建议每拿到一批新数据就重训一次（Q4 选的是“全部数据”，正好适合这个节奏）；页面上「向前验证」会显示它是“训练→哪一天”，可以直接对着看。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>接入前必须先定的两件事</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>① 方向偏涨时，密度到底动不动（默认不动？还是按现在那套 Δρ=min(|ΔA|/15, 0.03) 规则动）；② 动多少 —— 方向没有幅度信息，只能给“一个步长”，要现场先认可那个步长。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>你要怎么回答</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>A 现在就接进操作提示；B 先只展示（我建议这个）；C 先关掉别显示。回一句 A/B/C 即可。</t>
         </is>
